--- a/Assets/Game/luban/config/beans.xlsx
+++ b/Assets/Game/luban/config/beans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -98,43 +98,58 @@
     <t>注释</t>
   </si>
   <si>
-    <t>test.bean</t>
-  </si>
-  <si>
-    <t>这是个测试excel结构</t>
-  </si>
-  <si>
-    <t>x1</t>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>区间</t>
+  </si>
+  <si>
+    <t>min</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>黑色的</t>
-  </si>
-  <si>
-    <t>x3</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>x4</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>最差品质</t>
+    <t>最小值</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>最大值</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>道具id</t>
+  </si>
+  <si>
+    <t>item_count</t>
+  </si>
+  <si>
+    <t>道具数量</t>
+  </si>
+  <si>
+    <t>priority_item</t>
+  </si>
+  <si>
+    <t>带优先级的物品</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>优先级</t>
   </si>
 </sst>
 </file>
@@ -1213,61 +1228,107 @@
       <c r="B4" t="s">
         <v>23</v>
       </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="J5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="J6" t="s">
+    <row r="7" spans="1:16">
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
       <c r="J7" t="s">
         <v>33</v>
       </c>
       <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s">
         <v>34</v>
       </c>
-      <c r="M7" t="s">
+    </row>
+    <row r="8" spans="1:16">
+      <c r="J8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="K8" s="2"/>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="B12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="M12" s="4"/>
+      <c r="J12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="J13" s="2"/>

--- a/Assets/Game/luban/config/beans.xlsx
+++ b/Assets/Game/luban/config/beans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="22245" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Game/luban/config/beans.xlsx
+++ b/Assets/Game/luban/config/beans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22245" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +150,24 @@
   </si>
   <si>
     <t>优先级</t>
+  </si>
+  <si>
+    <t>attribute_bonus</t>
+  </si>
+  <si>
+    <t>属性加成</t>
+  </si>
+  <si>
+    <t>attribute_type</t>
+  </si>
+  <si>
+    <t>属性类型</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>值</t>
   </si>
 </sst>
 </file>
@@ -1336,14 +1354,35 @@
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="16" spans="1:16">
       <c r="J16" s="2"/>
